--- a/output/pdf_financials_xlsx/ETF.xlsx
+++ b/output/pdf_financials_xlsx/ETF.xlsx
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.114276</v>
+        <v>-0.114276</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.249153</v>
+        <v>-0.249153</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.060318</v>
@@ -1384,13 +1384,13 @@
         <v>0.026909</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.029196</v>
+        <v>-0.029196</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.226954</v>
+        <v>-0.226954</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.192572</v>
+        <v>-0.192572</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.114276</v>
+        <v>-0.114276</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.249153</v>
+        <v>-0.249153</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.060318</v>
@@ -1708,13 +1708,13 @@
         <v>0.026909</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.029196</v>
+        <v>-0.029196</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.226954</v>
+        <v>-0.226954</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.192572</v>
+        <v>-0.192572</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.114276</v>
+        <v>-0.114276</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.249153</v>
+        <v>-0.249153</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.060318</v>
@@ -1907,13 +1907,13 @@
         <v>0.026909</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.029196</v>
+        <v>-0.029196</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.226954</v>
+        <v>-0.226954</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.192572</v>
+        <v>-0.192572</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.114276</v>
+        <v>-0.114276</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.249153</v>
+        <v>-0.249153</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.060318</v>
@@ -2205,13 +2205,13 @@
         <v>0.026909</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.029196</v>
+        <v>-0.029196</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.226954</v>
+        <v>-0.226954</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.192572</v>
+        <v>-0.192572</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.114276</v>
+        <v>-0.114276</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.249153</v>
+        <v>-0.249153</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.060318</v>
@@ -2335,13 +2335,13 @@
         <v>0.026909</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.029196</v>
+        <v>-0.029196</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.226954</v>
+        <v>-0.226954</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.221816</v>
+        <v>-0.163328</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -2499,13 +2499,13 @@
         <v>0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="1" t="inlineStr">
         <is>
@@ -6400,55 +6400,55 @@
         <v>0.639074</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.6858919999999999</v>
+        <v>0.057168</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.6858919999999999</v>
+        <v>0.057168</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.057168</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.057168</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.057168</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.057168</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.057168</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.057168</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.057168</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.057168</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.057168</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.057168</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.16234</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.16234</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.16234</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.16234</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>0.16234</v>
       </c>
     </row>
     <row r="93">
@@ -8010,19 +8010,19 @@
         <v>0</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.482149</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.091738</v>
+        <v>-0.07811800000000001</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.07630199999999999</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0.302079</v>
+        <v>0.183304</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>-0.1078</v>
+        <v>-0.258464</v>
       </c>
     </row>
     <row r="119">
@@ -10702,7 +10702,11 @@
           <t>Warrant reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -17324,7 +17328,11 @@
           <t>Warrant reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -22622,7 +22630,11 @@
           <t>Warrant reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -25688,7 +25700,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -47921,13 +47937,13 @@
         </is>
       </c>
       <c r="N383" s="5" t="n">
-        <v>0.029196</v>
+        <v>-0.029196</v>
       </c>
       <c r="O383" s="5" t="n">
-        <v>0.226954</v>
+        <v>-0.226954</v>
       </c>
       <c r="P383" s="5" t="n">
-        <v>0.192572</v>
+        <v>-0.192572</v>
       </c>
       <c r="Q383" t="inlineStr">
         <is>
@@ -61188,13 +61204,13 @@
         </is>
       </c>
       <c r="E511" s="5" t="n">
-        <v>0.114276</v>
+        <v>-0.114276</v>
       </c>
       <c r="F511" s="5" t="n">
-        <v>0.249153</v>
+        <v>-0.249153</v>
       </c>
       <c r="G511" s="5" t="n">
-        <v>0.060318</v>
+        <v>-0.060318</v>
       </c>
       <c r="H511" t="inlineStr">
         <is>
@@ -61712,13 +61728,13 @@
         </is>
       </c>
       <c r="E516" s="5" t="n">
-        <v>0.114276</v>
+        <v>-0.114276</v>
       </c>
       <c r="F516" s="5" t="n">
-        <v>0.249153</v>
+        <v>-0.249153</v>
       </c>
       <c r="G516" s="5" t="n">
-        <v>0.060318</v>
+        <v>-0.060318</v>
       </c>
       <c r="H516" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ETF.xlsx
+++ b/output/pdf_financials_xlsx/ETF.xlsx
@@ -1105,40 +1105,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.016134</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003415</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.006548</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001329</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.025025</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.028293</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.033857</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.034648</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.023476</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.041567</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.032902</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.016367</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00037</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003641</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004168</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004168</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004153</v>
       </c>
     </row>
     <row r="13">
@@ -2178,40 +2178,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.114276</v>
+        <v>-0.09814199999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.249153</v>
+        <v>-0.245738</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.060318</v>
+        <v>-0.06686599999999999</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.575648</v>
+        <v>0.574319</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.194445</v>
+        <v>2.16942</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.150553</v>
+        <v>-0.178846</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.117209</v>
+        <v>-0.151066</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.1308</v>
+        <v>-0.165448</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.026909</v>
+        <v>0.003433</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.029196</v>
+        <v>0.012371</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.226954</v>
+        <v>-0.194052</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.192572</v>
+        <v>-0.176205</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.52925</v>
+        <v>0.52962</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.300555</v>
+        <v>0.304196</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.321315</v>
+        <v>0.325483</v>
       </c>
       <c r="R27" s="1" t="inlineStr">
         <is>
@@ -2308,40 +2308,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.114276</v>
+        <v>-0.09814199999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.249153</v>
+        <v>-0.245738</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.060318</v>
+        <v>-0.06686599999999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.575648</v>
+        <v>0.574319</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.194445</v>
+        <v>2.16942</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.150553</v>
+        <v>-0.178846</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.117209</v>
+        <v>-0.151066</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.1308</v>
+        <v>-0.165448</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.026909</v>
+        <v>0.003433</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.029196</v>
+        <v>0.012371</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.226954</v>
+        <v>-0.194052</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.163328</v>
+        <v>-0.146961</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2349,13 +2349,13 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.561234</v>
+        <v>0.561604</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.334241</v>
+        <v>0.337882</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.363514</v>
+        <v>0.367682</v>
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
@@ -2679,22 +2679,22 @@
         <v>0.271396</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.258183</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.111271</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.175702</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.065318</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.024631</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.691196</v>
       </c>
     </row>
     <row r="35">
@@ -2801,22 +2801,22 @@
         <v>0.271396</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.258183</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.111271</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.175702</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.065318</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.024631</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.691196</v>
       </c>
     </row>
     <row r="37">
@@ -3533,22 +3533,22 @@
         <v>0.06446399999999999</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.283456</v>
+        <v>0.025273</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.131518</v>
+        <v>0.020247</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.189327</v>
+        <v>0.013625</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.417678</v>
+        <v>0.35236</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.277481</v>
+        <v>0.25285</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>1.184915</v>
+        <v>0.493719</v>
       </c>
     </row>
     <row r="49">
@@ -8370,25 +8370,25 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.035143</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.038678</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.039991</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.02333</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.05255</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.064667</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-0.021129</v>
       </c>
     </row>
     <row r="125">
@@ -8431,25 +8431,25 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.035143</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.038678</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.039991</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.02333</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.05255</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.064667</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-0.021129</v>
       </c>
     </row>
     <row r="126">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -26376,7 +26376,11 @@
           <t>Net lease payments</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -42226,7 +42230,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -44166,7 +44170,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -47464,7 +47468,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -51014,7 +51018,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -60576,7 +60580,7 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E505" s="5" t="n">

--- a/output/pdf_financials_xlsx/ETF.xlsx
+++ b/output/pdf_financials_xlsx/ETF.xlsx
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.169846</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-0</v>
@@ -1721,10 +1721,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>-0.6405960000000001</v>
       </c>
       <c r="P20" s="1" t="inlineStr">
         <is>
@@ -1915,13 +1913,11 @@
       <c r="M23" s="3" t="n">
         <v>-0.192572</v>
       </c>
-      <c r="N23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N23" s="3" t="n">
+        <v>0.456406</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.52925</v>
+        <v>-0.6405960000000001</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>0.300555</v>
@@ -2513,7 +2509,7 @@
         </is>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>221.0384506376949</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0</v>
@@ -6841,13 +6837,11 @@
       <c r="M99" s="3" t="n">
         <v>-0.192572</v>
       </c>
-      <c r="N99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N99" s="3" t="n">
+        <v>0.456406</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>0.52925</v>
+        <v>-0.6405960000000001</v>
       </c>
       <c r="P99" s="3" t="n">
         <v>0.300555</v>
@@ -7544,46 +7538,46 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001019</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000962</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000684</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000432</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000771</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000846</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000848</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000886</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000691</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.0016</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00115</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005202</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000883</v>
       </c>
       <c r="P111" s="3" t="n">
         <v>0</v>
@@ -7763,10 +7757,10 @@
         <v>0</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="P114" s="3" t="n">
         <v>0</v>
@@ -7788,16 +7782,16 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.063294</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.140248</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.176419</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.151616</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -7821,25 +7815,25 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.130761</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.31096</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="P115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.093782</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.046894</v>
       </c>
       <c r="S115" s="3" t="n">
-        <v>0</v>
+        <v>0.115653</v>
       </c>
     </row>
     <row r="116">
@@ -8993,46 +8987,46 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001019</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000962</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000684</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000432</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000771</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000846</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000848</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000886</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000691</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.0016</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00115</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005202</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000883</v>
       </c>
       <c r="P134" s="3" t="n">
         <v>0</v>
@@ -9079,31 +9073,31 @@
         </is>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.122735</v>
+        <v>-0.123506</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.09833699999999999</v>
+        <v>-0.09918299999999999</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.09982099999999999</v>
+        <v>-0.100669</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-0.095087</v>
+        <v>-0.095973</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.09413100000000001</v>
+        <v>-0.094822</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-0.09492200000000001</v>
+        <v>-0.096522</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-0.134892</v>
+        <v>-0.136042</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-0.088353</v>
+        <v>-0.093555</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-0.166356</v>
+        <v>-0.167239</v>
       </c>
       <c r="P135" s="3" t="n">
         <v>-0.170882</v>
@@ -26004,7 +25998,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E168" s="5" t="n">
         <v>0.063294</v>
       </c>
@@ -28224,7 +28222,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E190" s="5" t="n">
         <v>-0.001019</v>
       </c>
@@ -28410,7 +28412,11 @@
           <t>Acquisition of investments</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -28606,7 +28612,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -29796,7 +29806,11 @@
           <t>Sale (acquisition) of investments</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -32290,7 +32304,11 @@
           <t>Net income/(loss) $</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
